--- a/MomijiStore_OS/01_InventoryManagement/SourceData/商品マスター_単品_v1.0.xlsx
+++ b/MomijiStore_OS/01_InventoryManagement/SourceData/商品マスター_単品_v1.0.xlsx
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>218</v>
+        <v>109</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2608,10 +2608,14 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>原価をKPI7月に合わせて更新</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -3784,7 +3788,9 @@
           <t>単品</t>
         </is>
       </c>
-      <c r="E72" s="2" t="n"/>
+      <c r="E72" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
           <t>楽天</t>
@@ -3802,10 +3808,14 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>原価をKPI7月に合わせて更新</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -4378,7 +4388,9 @@
           <t>単品</t>
         </is>
       </c>
-      <c r="E85" s="3" t="n"/>
+      <c r="E85" s="3" t="n">
+        <v>4382</v>
+      </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
           <t>楽天</t>
@@ -4396,10 +4408,14 @@
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="J85" s="3" t="inlineStr"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>原価をKPI7月に合わせて更新</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5113,7 +5129,7 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>2990</v>
+        <v>2690</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -5132,10 +5148,14 @@
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>原価をKPI7月に合わせて更新</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -9023,7 +9043,7 @@
         </is>
       </c>
       <c r="E186" s="2" t="n">
-        <v>19800</v>
+        <v>23979</v>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
@@ -9042,10 +9062,14 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="inlineStr"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>原価をKPI7月に合わせて更新</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -9803,7 +9827,7 @@
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>454</v>
+        <v>306</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -9822,10 +9846,14 @@
       </c>
       <c r="I203" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="J203" s="3" t="inlineStr"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J203" s="3" t="inlineStr">
+        <is>
+          <t>原価をKPI7月に合わせて更新</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -10033,7 +10061,7 @@
         </is>
       </c>
       <c r="E208" s="2" t="n">
-        <v>25580</v>
+        <v>25800</v>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
@@ -10052,10 +10080,14 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="J208" s="2" t="inlineStr"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>原価をKPI7月に合わせて更新</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -10723,7 +10755,7 @@
         </is>
       </c>
       <c r="E223" s="3" t="n">
-        <v>5490</v>
+        <v>6490</v>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
@@ -10742,10 +10774,14 @@
       </c>
       <c r="I223" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="J223" s="3" t="inlineStr"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J223" s="3" t="inlineStr">
+        <is>
+          <t>原価をKPI7月に合わせて更新</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -13345,7 +13381,7 @@
         </is>
       </c>
       <c r="E280" s="2" t="n">
-        <v>693</v>
+        <v>495</v>
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
@@ -13364,10 +13400,14 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="J280" s="2" t="inlineStr"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr">
+        <is>
+          <t>原価をKPI7月に合わせて更新</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
@@ -13437,7 +13477,7 @@
         </is>
       </c>
       <c r="E282" s="2" t="n">
-        <v>1287</v>
+        <v>1155</v>
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
@@ -13456,10 +13496,14 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="J282" s="2" t="inlineStr"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr">
+        <is>
+          <t>原価をKPI7月に合わせて更新</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
@@ -14035,7 +14079,7 @@
         </is>
       </c>
       <c r="E295" s="3" t="n">
-        <v>672</v>
+        <v>1008</v>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
@@ -14054,10 +14098,14 @@
       </c>
       <c r="I295" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="J295" s="3" t="inlineStr"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J295" s="3" t="inlineStr">
+        <is>
+          <t>原価をKPI7月に合わせて更新</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -17013,7 +17061,7 @@
         </is>
       </c>
       <c r="E360" s="2" t="n">
-        <v>572</v>
+        <v>297</v>
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
@@ -17032,10 +17080,14 @@
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="J360" s="2" t="inlineStr"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr">
+        <is>
+          <t>原価をKPI7月に合わせて更新</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
